--- a/owlcms/src/main/resources/templates/timing/TimingStats.xlsx
+++ b/owlcms/src/main/resources/templates/timing/TimingStats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\timing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7A7C90-A375-4905-B598-C97B9ADD5AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF51D7A-FDE5-4662-9564-043E84F6F174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25335" yWindow="1980" windowWidth="24615" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24990" yWindow="2325" windowWidth="24615" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Données" sheetId="1" r:id="rId1"/>
@@ -205,7 +205,7 @@
     <t>Session Timing Summary</t>
   </si>
   <si>
-    <t>Note: Use Ctrl+Alt+F9 to compute the values (Command-Option-F9 on Mac)</t>
+    <t>Note: In Excel, use Ctrl+Alt+F9 to recompute the values (Ctrl-Option-F9 on Mac)</t>
   </si>
 </sst>
 </file>
@@ -662,9 +662,6 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -677,6 +674,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
@@ -1223,19 +1223,19 @@
       <c r="A5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
       <c r="M5" s="14"/>
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
@@ -1379,24 +1379,24 @@
       <c r="R10" s="32"/>
       <c r="S10" s="32"/>
     </row>
-    <row r="11" spans="1:19" s="56" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="57" t="s">
+    <row r="11" spans="1:19" s="55" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60"/>
-      <c r="P11" s="60"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="59"/>
+      <c r="P11" s="59"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D12" s="1"/>
